--- a/output/pdf_financials_xlsx/RUU.xlsx
+++ b/output/pdf_financials_xlsx/RUU.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.371999</v>
+        <v>0.859038</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.161892</v>
+        <v>0.339569</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.323937</v>
+        <v>1.425835</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.371999</v>
+        <v>-0.859038</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.161892</v>
+        <v>-0.339569</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.323937</v>
+        <v>-1.425835</v>
       </c>
     </row>
     <row r="12">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.122851</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.173192</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.032944</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.122851</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.173192</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.032944</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.122851</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.273192</v>
+        <v>0.1</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07265000000000001</v>
+        <v>0.039706</v>
       </c>
     </row>
     <row r="49">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4385,17 +4385,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>-0.859038</v>
+        <v>0.859038</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.339569</v>
+        <v>0.339569</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-1.425835</v>
+        <v>1.425835</v>
       </c>
     </row>
     <row r="59">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">

--- a/output/pdf_financials_xlsx/RUU.xlsx
+++ b/output/pdf_financials_xlsx/RUU.xlsx
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.063831</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.140604</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.05145</v>
       </c>
     </row>
     <row r="102">
@@ -2161,13 +2161,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.289685</v>
+        <v>-0.225854</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.01378</v>
+        <v>0.154384</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.133462</v>
+        <v>0.082012</v>
       </c>
     </row>
     <row r="107">
@@ -3545,7 +3545,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.063831</v>
       </c>
